--- a/대시보드노출제외상품.xlsx
+++ b/대시보드노출제외상품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UNIX117\♥Claude\02_Issue별\06_Stock-Supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3419364B-B44D-4BF0-9ABA-5DF9E366CCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C07B0D9-EC96-4D6D-A417-E666FD052BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7B9D2AA-30FD-4CA4-BC5E-D41084FA95F9}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
   <si>
     <t>제품명</t>
   </si>
@@ -226,6 +226,9 @@
   <si>
     <t>UCI-A4140</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PW-A5926</t>
   </si>
 </sst>
 </file>
@@ -379,6 +382,7 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
+          <cell r="B3"/>
           <cell r="C3">
             <v>2</v>
           </cell>
@@ -7498,6 +7502,8 @@
           <cell r="F312" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G312"/>
+          <cell r="H312"/>
         </row>
         <row r="313">
           <cell r="B313" t="str">
@@ -7515,6 +7521,8 @@
           <cell r="F313" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G313"/>
+          <cell r="H313"/>
         </row>
         <row r="314">
           <cell r="B314" t="str">
@@ -7532,6 +7540,8 @@
           <cell r="F314" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G314"/>
+          <cell r="H314"/>
         </row>
         <row r="315">
           <cell r="B315" t="str">
@@ -7549,6 +7559,8 @@
           <cell r="F315" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G315"/>
+          <cell r="H315"/>
         </row>
         <row r="316">
           <cell r="B316" t="str">
@@ -7566,6 +7578,8 @@
           <cell r="F316" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G316"/>
+          <cell r="H316"/>
         </row>
         <row r="317">
           <cell r="B317" t="str">
@@ -7583,6 +7597,8 @@
           <cell r="F317" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G317"/>
+          <cell r="H317"/>
         </row>
         <row r="318">
           <cell r="B318" t="str">
@@ -7600,6 +7616,8 @@
           <cell r="F318" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G318"/>
+          <cell r="H318"/>
         </row>
         <row r="319">
           <cell r="B319" t="str">
@@ -7617,6 +7635,8 @@
           <cell r="F319" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G319"/>
+          <cell r="H319"/>
         </row>
         <row r="320">
           <cell r="B320" t="str">
@@ -7634,6 +7654,8 @@
           <cell r="F320" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G320"/>
+          <cell r="H320"/>
         </row>
         <row r="321">
           <cell r="B321" t="str">
@@ -7651,6 +7673,8 @@
           <cell r="F321" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G321"/>
+          <cell r="H321"/>
         </row>
         <row r="322">
           <cell r="B322" t="str">
@@ -7668,6 +7692,8 @@
           <cell r="F322" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G322"/>
+          <cell r="H322"/>
         </row>
         <row r="323">
           <cell r="B323" t="str">
@@ -7685,6 +7711,8 @@
           <cell r="F323" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G323"/>
+          <cell r="H323"/>
         </row>
         <row r="324">
           <cell r="B324" t="str">
@@ -7702,6 +7730,8 @@
           <cell r="F324" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G324"/>
+          <cell r="H324"/>
         </row>
         <row r="325">
           <cell r="B325" t="str">
@@ -7719,6 +7749,8 @@
           <cell r="F325" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G325"/>
+          <cell r="H325"/>
         </row>
         <row r="326">
           <cell r="B326" t="str">
@@ -7736,6 +7768,8 @@
           <cell r="F326" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G326"/>
+          <cell r="H326"/>
         </row>
         <row r="327">
           <cell r="B327" t="str">
@@ -7753,6 +7787,8 @@
           <cell r="F327" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G327"/>
+          <cell r="H327"/>
         </row>
         <row r="328">
           <cell r="B328" t="str">
@@ -7770,6 +7806,8 @@
           <cell r="F328" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G328"/>
+          <cell r="H328"/>
         </row>
         <row r="329">
           <cell r="B329" t="str">
@@ -7787,6 +7825,8 @@
           <cell r="F329" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G329"/>
+          <cell r="H329"/>
         </row>
         <row r="330">
           <cell r="B330" t="str">
@@ -7804,6 +7844,8 @@
           <cell r="F330" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G330"/>
+          <cell r="H330"/>
         </row>
         <row r="331">
           <cell r="B331" t="str">
@@ -7821,6 +7863,8 @@
           <cell r="F331" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G331"/>
+          <cell r="H331"/>
         </row>
         <row r="332">
           <cell r="B332" t="str">
@@ -7838,6 +7882,8 @@
           <cell r="F332" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G332"/>
+          <cell r="H332"/>
         </row>
         <row r="333">
           <cell r="B333" t="str">
@@ -7855,6 +7901,8 @@
           <cell r="F333" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G333"/>
+          <cell r="H333"/>
         </row>
         <row r="334">
           <cell r="B334" t="str">
@@ -7872,6 +7920,8 @@
           <cell r="F334" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G334"/>
+          <cell r="H334"/>
         </row>
         <row r="335">
           <cell r="B335" t="str">
@@ -7889,6 +7939,8 @@
           <cell r="F335" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G335"/>
+          <cell r="H335"/>
         </row>
         <row r="336">
           <cell r="B336" t="str">
@@ -7906,6 +7958,8 @@
           <cell r="F336" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G336"/>
+          <cell r="H336"/>
         </row>
         <row r="337">
           <cell r="B337" t="str">
@@ -7923,6 +7977,8 @@
           <cell r="F337" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G337"/>
+          <cell r="H337"/>
         </row>
         <row r="338">
           <cell r="B338" t="str">
@@ -7940,6 +7996,8 @@
           <cell r="F338" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G338"/>
+          <cell r="H338"/>
         </row>
         <row r="339">
           <cell r="B339" t="str">
@@ -7957,6 +8015,8 @@
           <cell r="F339" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G339"/>
+          <cell r="H339"/>
         </row>
         <row r="340">
           <cell r="B340" t="str">
@@ -7974,6 +8034,8 @@
           <cell r="F340" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G340"/>
+          <cell r="H340"/>
         </row>
         <row r="341">
           <cell r="B341" t="str">
@@ -7991,6 +8053,8 @@
           <cell r="F341" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G341"/>
+          <cell r="H341"/>
         </row>
         <row r="342">
           <cell r="B342" t="str">
@@ -8008,6 +8072,8 @@
           <cell r="F342" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G342"/>
+          <cell r="H342"/>
         </row>
         <row r="343">
           <cell r="B343" t="str">
@@ -10029,6 +10095,7 @@
           <cell r="G430">
             <v>88</v>
           </cell>
+          <cell r="H430"/>
         </row>
         <row r="431">
           <cell r="B431" t="str">
@@ -10049,6 +10116,7 @@
           <cell r="G431">
             <v>88</v>
           </cell>
+          <cell r="H431"/>
         </row>
         <row r="432">
           <cell r="B432" t="str">
@@ -10069,6 +10137,7 @@
           <cell r="G432">
             <v>88</v>
           </cell>
+          <cell r="H432"/>
         </row>
         <row r="433">
           <cell r="B433" t="str">
@@ -10089,6 +10158,7 @@
           <cell r="G433">
             <v>88</v>
           </cell>
+          <cell r="H433"/>
         </row>
         <row r="434">
           <cell r="B434" t="str">
@@ -10109,6 +10179,7 @@
           <cell r="G434">
             <v>88</v>
           </cell>
+          <cell r="H434"/>
         </row>
         <row r="435">
           <cell r="B435" t="str">
@@ -10129,6 +10200,7 @@
           <cell r="G435">
             <v>88</v>
           </cell>
+          <cell r="H435"/>
         </row>
         <row r="436">
           <cell r="B436" t="str">
@@ -10149,6 +10221,7 @@
           <cell r="G436">
             <v>88</v>
           </cell>
+          <cell r="H436"/>
         </row>
         <row r="437">
           <cell r="B437" t="str">
@@ -10169,6 +10242,7 @@
           <cell r="G437">
             <v>88</v>
           </cell>
+          <cell r="H437"/>
         </row>
         <row r="438">
           <cell r="B438" t="str">
@@ -10189,6 +10263,7 @@
           <cell r="G438">
             <v>88</v>
           </cell>
+          <cell r="H438"/>
         </row>
         <row r="439">
           <cell r="B439" t="str">
@@ -10209,6 +10284,7 @@
           <cell r="G439">
             <v>88</v>
           </cell>
+          <cell r="H439"/>
         </row>
         <row r="440">
           <cell r="B440" t="str">
@@ -10229,6 +10305,7 @@
           <cell r="G440">
             <v>88</v>
           </cell>
+          <cell r="H440"/>
         </row>
         <row r="441">
           <cell r="B441" t="str">
@@ -10249,6 +10326,7 @@
           <cell r="G441">
             <v>88</v>
           </cell>
+          <cell r="H441"/>
         </row>
         <row r="442">
           <cell r="B442" t="str">
@@ -10269,6 +10347,7 @@
           <cell r="G442">
             <v>88</v>
           </cell>
+          <cell r="H442"/>
         </row>
         <row r="443">
           <cell r="B443" t="str">
@@ -10289,6 +10368,7 @@
           <cell r="G443">
             <v>88</v>
           </cell>
+          <cell r="H443"/>
         </row>
         <row r="444">
           <cell r="B444" t="str">
@@ -10309,6 +10389,7 @@
           <cell r="G444">
             <v>88</v>
           </cell>
+          <cell r="H444"/>
         </row>
         <row r="445">
           <cell r="B445" t="str">
@@ -10329,6 +10410,7 @@
           <cell r="G445">
             <v>88</v>
           </cell>
+          <cell r="H445"/>
         </row>
         <row r="446">
           <cell r="B446" t="str">
@@ -10349,6 +10431,7 @@
           <cell r="G446">
             <v>88</v>
           </cell>
+          <cell r="H446"/>
         </row>
         <row r="447">
           <cell r="B447" t="str">
@@ -10504,6 +10587,8 @@
           <cell r="F453" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G453"/>
+          <cell r="H453"/>
         </row>
         <row r="454">
           <cell r="B454" t="str">
@@ -10521,6 +10606,8 @@
           <cell r="F454" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G454"/>
+          <cell r="H454"/>
         </row>
         <row r="455">
           <cell r="B455" t="str">
@@ -10538,6 +10625,8 @@
           <cell r="F455" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G455"/>
+          <cell r="H455"/>
         </row>
         <row r="456">
           <cell r="B456" t="str">
@@ -10555,6 +10644,8 @@
           <cell r="F456" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G456"/>
+          <cell r="H456"/>
         </row>
         <row r="457">
           <cell r="B457" t="str">
@@ -10572,6 +10663,8 @@
           <cell r="F457" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G457"/>
+          <cell r="H457"/>
         </row>
         <row r="458">
           <cell r="B458" t="str">
@@ -10589,6 +10682,8 @@
           <cell r="F458" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G458"/>
+          <cell r="H458"/>
         </row>
         <row r="459">
           <cell r="B459" t="str">
@@ -10606,6 +10701,8 @@
           <cell r="F459" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G459"/>
+          <cell r="H459"/>
         </row>
         <row r="460">
           <cell r="B460" t="str">
@@ -10623,6 +10720,8 @@
           <cell r="F460" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G460"/>
+          <cell r="H460"/>
         </row>
         <row r="461">
           <cell r="B461" t="str">
@@ -10640,6 +10739,8 @@
           <cell r="F461" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G461"/>
+          <cell r="H461"/>
         </row>
         <row r="462">
           <cell r="B462" t="str">
@@ -10657,6 +10758,8 @@
           <cell r="F462" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G462"/>
+          <cell r="H462"/>
         </row>
         <row r="463">
           <cell r="B463" t="str">
@@ -10674,6 +10777,8 @@
           <cell r="F463" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G463"/>
+          <cell r="H463"/>
         </row>
         <row r="464">
           <cell r="B464" t="str">
@@ -10691,6 +10796,8 @@
           <cell r="F464" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G464"/>
+          <cell r="H464"/>
         </row>
         <row r="465">
           <cell r="B465" t="str">
@@ -10708,6 +10815,8 @@
           <cell r="F465" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G465"/>
+          <cell r="H465"/>
         </row>
         <row r="466">
           <cell r="B466" t="str">
@@ -10725,6 +10834,8 @@
           <cell r="F466" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G466"/>
+          <cell r="H466"/>
         </row>
         <row r="467">
           <cell r="B467" t="str">
@@ -10742,6 +10853,8 @@
           <cell r="F467" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G467"/>
+          <cell r="H467"/>
         </row>
         <row r="468">
           <cell r="B468" t="str">
@@ -10759,6 +10872,8 @@
           <cell r="F468" t="str">
             <v>단종</v>
           </cell>
+          <cell r="G468"/>
+          <cell r="H468"/>
         </row>
         <row r="469">
           <cell r="B469" t="str">
@@ -10776,6 +10891,8 @@
           <cell r="F469" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G469"/>
+          <cell r="H469"/>
         </row>
         <row r="470">
           <cell r="B470" t="str">
@@ -10793,6 +10910,8 @@
           <cell r="F470" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G470"/>
+          <cell r="H470"/>
         </row>
         <row r="471">
           <cell r="B471" t="str">
@@ -10810,6 +10929,8 @@
           <cell r="F471" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G471"/>
+          <cell r="H471"/>
         </row>
         <row r="472">
           <cell r="B472" t="str">
@@ -10827,6 +10948,8 @@
           <cell r="F472" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G472"/>
+          <cell r="H472"/>
         </row>
         <row r="473">
           <cell r="B473" t="str">
@@ -10844,6 +10967,8 @@
           <cell r="F473" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G473"/>
+          <cell r="H473"/>
         </row>
         <row r="474">
           <cell r="B474" t="str">
@@ -10861,6 +10986,8 @@
           <cell r="F474" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G474"/>
+          <cell r="H474"/>
         </row>
         <row r="475">
           <cell r="B475" t="str">
@@ -10878,6 +11005,8 @@
           <cell r="F475" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G475"/>
+          <cell r="H475"/>
         </row>
         <row r="476">
           <cell r="B476" t="str">
@@ -10895,6 +11024,8 @@
           <cell r="F476" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G476"/>
+          <cell r="H476"/>
         </row>
         <row r="477">
           <cell r="B477" t="str">
@@ -10912,6 +11043,8 @@
           <cell r="F477" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G477"/>
+          <cell r="H477"/>
         </row>
         <row r="478">
           <cell r="B478" t="str">
@@ -10929,6 +11062,8 @@
           <cell r="F478" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G478"/>
+          <cell r="H478"/>
         </row>
         <row r="479">
           <cell r="B479" t="str">
@@ -10946,6 +11081,8 @@
           <cell r="F479" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G479"/>
+          <cell r="H479"/>
         </row>
         <row r="480">
           <cell r="B480" t="str">
@@ -10963,6 +11100,8 @@
           <cell r="F480" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G480"/>
+          <cell r="H480"/>
         </row>
         <row r="481">
           <cell r="B481" t="str">
@@ -10980,6 +11119,8 @@
           <cell r="F481" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G481"/>
+          <cell r="H481"/>
         </row>
         <row r="482">
           <cell r="B482" t="str">
@@ -10997,6 +11138,8 @@
           <cell r="F482" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G482"/>
+          <cell r="H482"/>
         </row>
         <row r="483">
           <cell r="B483" t="str">
@@ -11014,6 +11157,8 @@
           <cell r="F483" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G483"/>
+          <cell r="H483"/>
         </row>
         <row r="484">
           <cell r="B484" t="str">
@@ -11031,6 +11176,8 @@
           <cell r="F484" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G484"/>
+          <cell r="H484"/>
         </row>
         <row r="485">
           <cell r="B485" t="str">
@@ -11048,6 +11195,8 @@
           <cell r="F485" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G485"/>
+          <cell r="H485"/>
         </row>
         <row r="486">
           <cell r="B486" t="str">
@@ -11065,6 +11214,8 @@
           <cell r="F486" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G486"/>
+          <cell r="H486"/>
         </row>
         <row r="487">
           <cell r="B487" t="str">
@@ -11082,6 +11233,8 @@
           <cell r="F487" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G487"/>
+          <cell r="H487"/>
         </row>
         <row r="488">
           <cell r="B488" t="str">
@@ -11099,6 +11252,8 @@
           <cell r="F488" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G488"/>
+          <cell r="H488"/>
         </row>
         <row r="489">
           <cell r="B489" t="str">
@@ -11116,6 +11271,8 @@
           <cell r="F489" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G489"/>
+          <cell r="H489"/>
         </row>
         <row r="490">
           <cell r="B490" t="str">
@@ -11133,6 +11290,8 @@
           <cell r="F490" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G490"/>
+          <cell r="H490"/>
         </row>
         <row r="491">
           <cell r="B491" t="str">
@@ -11150,6 +11309,8 @@
           <cell r="F491" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G491"/>
+          <cell r="H491"/>
         </row>
         <row r="492">
           <cell r="B492" t="str">
@@ -11167,6 +11328,8 @@
           <cell r="F492" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G492"/>
+          <cell r="H492"/>
         </row>
         <row r="493">
           <cell r="B493" t="str">
@@ -11184,6 +11347,8 @@
           <cell r="F493" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G493"/>
+          <cell r="H493"/>
         </row>
         <row r="494">
           <cell r="B494" t="str">
@@ -11201,6 +11366,8 @@
           <cell r="F494" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G494"/>
+          <cell r="H494"/>
         </row>
         <row r="495">
           <cell r="B495" t="str">
@@ -11218,6 +11385,8 @@
           <cell r="F495" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G495"/>
+          <cell r="H495"/>
         </row>
         <row r="496">
           <cell r="B496" t="str">
@@ -11235,6 +11404,8 @@
           <cell r="F496" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G496"/>
+          <cell r="H496"/>
         </row>
         <row r="497">
           <cell r="B497" t="str">
@@ -11252,6 +11423,8 @@
           <cell r="F497" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G497"/>
+          <cell r="H497"/>
         </row>
         <row r="498">
           <cell r="B498" t="str">
@@ -11269,6 +11442,8 @@
           <cell r="F498" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G498"/>
+          <cell r="H498"/>
         </row>
         <row r="499">
           <cell r="B499" t="str">
@@ -11286,6 +11461,8 @@
           <cell r="F499" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G499"/>
+          <cell r="H499"/>
         </row>
         <row r="500">
           <cell r="B500" t="str">
@@ -11303,6 +11480,8 @@
           <cell r="F500" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G500"/>
+          <cell r="H500"/>
         </row>
         <row r="501">
           <cell r="B501" t="str">
@@ -11320,6 +11499,8 @@
           <cell r="F501" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G501"/>
+          <cell r="H501"/>
         </row>
         <row r="502">
           <cell r="B502" t="str">
@@ -11337,6 +11518,8 @@
           <cell r="F502" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G502"/>
+          <cell r="H502"/>
         </row>
         <row r="503">
           <cell r="B503" t="str">
@@ -11354,6 +11537,8 @@
           <cell r="F503" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G503"/>
+          <cell r="H503"/>
         </row>
         <row r="504">
           <cell r="B504" t="str">
@@ -11371,6 +11556,8 @@
           <cell r="F504" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G504"/>
+          <cell r="H504"/>
         </row>
         <row r="505">
           <cell r="B505" t="str">
@@ -11388,6 +11575,8 @@
           <cell r="F505" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G505"/>
+          <cell r="H505"/>
         </row>
         <row r="506">
           <cell r="B506" t="str">
@@ -11405,6 +11594,8 @@
           <cell r="F506" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G506"/>
+          <cell r="H506"/>
         </row>
         <row r="507">
           <cell r="B507" t="str">
@@ -11422,6 +11613,8 @@
           <cell r="F507" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G507"/>
+          <cell r="H507"/>
         </row>
         <row r="508">
           <cell r="B508" t="str">
@@ -11439,6 +11632,8 @@
           <cell r="F508" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G508"/>
+          <cell r="H508"/>
         </row>
         <row r="509">
           <cell r="B509" t="str">
@@ -11456,6 +11651,8 @@
           <cell r="F509" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G509"/>
+          <cell r="H509"/>
         </row>
         <row r="510">
           <cell r="B510" t="str">
@@ -11473,6 +11670,8 @@
           <cell r="F510" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G510"/>
+          <cell r="H510"/>
         </row>
         <row r="511">
           <cell r="B511" t="str">
@@ -11490,6 +11689,16 @@
           <cell r="F511" t="str">
             <v>기타</v>
           </cell>
+          <cell r="G511"/>
+          <cell r="H511"/>
+        </row>
+        <row r="512">
+          <cell r="C512"/>
+          <cell r="D512"/>
+          <cell r="E512"/>
+          <cell r="F512"/>
+          <cell r="G512"/>
+          <cell r="H512"/>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
@@ -12323,14 +12532,36 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="A19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2">
+        <f>VLOOKUP($A19,[1]상품코드집!$B:$H,2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="str">
+        <f>VLOOKUP($A19,[1]상품코드집!$B:$H,3,0)</f>
+        <v>헤어롤</v>
+      </c>
+      <c r="D19" s="2">
+        <f>VLOOKUP($A19,[1]상품코드집!$B:$H,4,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f>VLOOKUP($A19,[1]상품코드집!$B:$H,5,0)</f>
+        <v>헤어롤</v>
+      </c>
+      <c r="F19" s="2">
+        <f>VLOOKUP($A19,[1]상품코드집!$B:$H,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="str">
+        <f>VLOOKUP($A19,[1]상품코드집!$B:$H,7,0)</f>
+        <v>헤어롤</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1"/>

--- a/대시보드노출제외상품.xlsx
+++ b/대시보드노출제외상품.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\UNIX117\♥Claude\02_Issue별\06_Stock-Supply\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C07B0D9-EC96-4D6D-A417-E666FD052BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E73A2F-A0B0-48FF-B28A-4301362C400D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7B9D2AA-30FD-4CA4-BC5E-D41084FA95F9}"/>
   </bookViews>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="43">
   <si>
     <t>제품명</t>
   </si>
@@ -229,6 +229,18 @@
   </si>
   <si>
     <t>PW-A5926</t>
+  </si>
+  <si>
+    <t>UCI-A2501NA</t>
+  </si>
+  <si>
+    <t>UCI-A4132N</t>
+  </si>
+  <si>
+    <t>UN-A3965</t>
+  </si>
+  <si>
+    <t>UN-B6011</t>
   </si>
 </sst>
 </file>
@@ -12564,44 +12576,132 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="A20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="2">
+        <f>VLOOKUP($A20,[1]상품코드집!$B:$H,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="C20" s="2" t="str">
+        <f>VLOOKUP($A20,[1]상품코드집!$B:$H,3,0)</f>
+        <v>고데기</v>
+      </c>
+      <c r="D20" s="2">
+        <f>VLOOKUP($A20,[1]상품코드집!$B:$H,4,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f>VLOOKUP($A20,[1]상품코드집!$B:$H,5,0)</f>
+        <v>테이크아웃</v>
+      </c>
+      <c r="F20" s="2">
+        <f>VLOOKUP($A20,[1]상품코드집!$B:$H,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="str">
+        <f>VLOOKUP($A20,[1]상품코드집!$B:$H,7,0)</f>
+        <v>테이크아웃2</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2">
+        <f>VLOOKUP($A21,[1]상품코드집!$B:$H,2,0)</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="2" t="str">
+        <f>VLOOKUP($A21,[1]상품코드집!$B:$H,3,0)</f>
+        <v>고데기</v>
+      </c>
+      <c r="D21" s="2">
+        <f>VLOOKUP($A21,[1]상품코드집!$B:$H,4,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f>VLOOKUP($A21,[1]상품코드집!$B:$H,5,0)</f>
+        <v>스타일팔레트</v>
+      </c>
+      <c r="F21" s="2">
+        <f>VLOOKUP($A21,[1]상품코드집!$B:$H,6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="str">
+        <f>VLOOKUP($A21,[1]상품코드집!$B:$H,7,0)</f>
+        <v>스타일팔레트</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2">
+        <f>VLOOKUP($A22,[1]상품코드집!$B:$H,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f>VLOOKUP($A22,[1]상품코드집!$B:$H,3,0)</f>
+        <v>드라이어</v>
+      </c>
+      <c r="D22" s="2">
+        <f>VLOOKUP($A22,[1]상품코드집!$B:$H,4,0)</f>
+        <v>6</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f>VLOOKUP($A22,[1]상품코드집!$B:$H,5,0)</f>
+        <v>가정용</v>
+      </c>
+      <c r="F22" s="2">
+        <f>VLOOKUP($A22,[1]상품코드집!$B:$H,6,0)</f>
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="str">
+        <f>VLOOKUP($A22,[1]상품코드집!$B:$H,7,0)</f>
+        <v>접이식(39S)</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2">
+        <f>VLOOKUP($A23,[1]상품코드집!$B:$H,2,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="str">
+        <f>VLOOKUP($A23,[1]상품코드집!$B:$H,3,0)</f>
+        <v>드라이어</v>
+      </c>
+      <c r="D23" s="2">
+        <f>VLOOKUP($A23,[1]상품코드집!$B:$H,4,0)</f>
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f>VLOOKUP($A23,[1]상품코드집!$B:$H,5,0)</f>
+        <v>BLDC</v>
+      </c>
+      <c r="F23" s="2">
+        <f>VLOOKUP($A23,[1]상품코드집!$B:$H,6,0)</f>
+        <v>3</v>
+      </c>
+      <c r="G23" s="2" t="str">
+        <f>VLOOKUP($A23,[1]상품코드집!$B:$H,7,0)</f>
+        <v>슈퍼D+/CHANGE</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1"/>
